--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-07-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E15C9A7-AC7B-4E42-9734-FE964904D134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA8B245-5968-4AB6-822B-6AC6D8BCFBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31140" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="376">
   <si>
     <t>SKU</t>
   </si>
@@ -928,45 +928,6 @@
     <t>£2,050.00</t>
   </si>
   <si>
-    <t>£15.61</t>
-  </si>
-  <si>
-    <t>£18.29</t>
-  </si>
-  <si>
-    <t>£22.48</t>
-  </si>
-  <si>
-    <t>£23.84</t>
-  </si>
-  <si>
-    <t>£30.39</t>
-  </si>
-  <si>
-    <t>£33.36</t>
-  </si>
-  <si>
-    <t>£37.12</t>
-  </si>
-  <si>
-    <t>£40.84</t>
-  </si>
-  <si>
-    <t>£40.35</t>
-  </si>
-  <si>
-    <t>£50.12</t>
-  </si>
-  <si>
-    <t>£59.62</t>
-  </si>
-  <si>
-    <t>£60.65</t>
-  </si>
-  <si>
-    <t>£60.40</t>
-  </si>
-  <si>
     <t>£1692.0</t>
   </si>
   <si>
@@ -1163,6 +1124,30 @@
   </si>
   <si>
     <t>£1,938.89</t>
+  </si>
+  <si>
+    <t>£21.43</t>
+  </si>
+  <si>
+    <t>£28.83</t>
+  </si>
+  <si>
+    <t>£32.44</t>
+  </si>
+  <si>
+    <t>£38.79</t>
+  </si>
+  <si>
+    <t>£48.84</t>
+  </si>
+  <si>
+    <t>£49.31</t>
+  </si>
+  <si>
+    <t>£59.02</t>
+  </si>
+  <si>
+    <t>£58.97</t>
   </si>
 </sst>
 </file>
@@ -1597,19 +1582,19 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="E2" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="F2" t="s">
         <v>279</v>
       </c>
       <c r="G2" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="H2" t="s">
         <v>86</v>
@@ -1618,7 +1603,7 @@
         <v>111</v>
       </c>
       <c r="J2" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="K2" t="s">
         <v>147</v>
@@ -1630,19 +1615,19 @@
         <v>173</v>
       </c>
       <c r="N2" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="O2" t="s">
         <v>202</v>
       </c>
       <c r="P2" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="Q2" t="s">
         <v>248</v>
       </c>
       <c r="R2" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1665,7 +1650,7 @@
         <v>280</v>
       </c>
       <c r="G3" t="s">
-        <v>303</v>
+        <v>203</v>
       </c>
       <c r="H3" t="s">
         <v>87</v>
@@ -1674,7 +1659,7 @@
         <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="K3" t="s">
         <v>148</v>
@@ -1686,7 +1671,7 @@
         <v>174</v>
       </c>
       <c r="N3" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="O3" t="s">
         <v>203</v>
@@ -1698,7 +1683,7 @@
         <v>249</v>
       </c>
       <c r="R3" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1709,19 +1694,19 @@
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="E4" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="F4" t="s">
         <v>281</v>
       </c>
       <c r="G4" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="H4" t="s">
         <v>88</v>
@@ -1730,7 +1715,7 @@
         <v>113</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="K4" t="s">
         <v>149</v>
@@ -1742,7 +1727,7 @@
         <v>175</v>
       </c>
       <c r="N4" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="O4" t="s">
         <v>204</v>
@@ -1754,7 +1739,7 @@
         <v>250</v>
       </c>
       <c r="R4" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1777,7 +1762,7 @@
         <v>282</v>
       </c>
       <c r="G5" t="s">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="H5" t="s">
         <v>89</v>
@@ -1798,7 +1783,7 @@
         <v>176</v>
       </c>
       <c r="N5" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="O5" t="s">
         <v>205</v>
@@ -1833,7 +1818,7 @@
         <v>283</v>
       </c>
       <c r="G6" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="H6" t="s">
         <v>90</v>
@@ -1854,7 +1839,7 @@
         <v>177</v>
       </c>
       <c r="N6" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="O6" t="s">
         <v>206</v>
@@ -1866,7 +1851,7 @@
         <v>252</v>
       </c>
       <c r="R6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1889,7 +1874,7 @@
         <v>284</v>
       </c>
       <c r="G7" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="H7" t="s">
         <v>91</v>
@@ -1910,7 +1895,7 @@
         <v>178</v>
       </c>
       <c r="N7" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="O7" t="s">
         <v>74</v>
@@ -1922,7 +1907,7 @@
         <v>253</v>
       </c>
       <c r="R7" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1933,19 +1918,19 @@
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="F8" t="s">
         <v>284</v>
       </c>
       <c r="G8" t="s">
-        <v>307</v>
+        <v>180</v>
       </c>
       <c r="H8" t="s">
         <v>91</v>
@@ -1966,7 +1951,7 @@
         <v>179</v>
       </c>
       <c r="N8" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="O8" t="s">
         <v>180</v>
@@ -1978,7 +1963,7 @@
         <v>254</v>
       </c>
       <c r="R8" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -2001,7 +1986,7 @@
         <v>285</v>
       </c>
       <c r="G9" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
         <v>92</v>
@@ -2010,7 +1995,7 @@
         <v>118</v>
       </c>
       <c r="J9" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="K9" t="s">
         <v>154</v>
@@ -2022,7 +2007,7 @@
         <v>180</v>
       </c>
       <c r="N9" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="O9" t="s">
         <v>75</v>
@@ -2057,7 +2042,7 @@
         <v>286</v>
       </c>
       <c r="G10" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="H10" t="s">
         <v>93</v>
@@ -2078,7 +2063,7 @@
         <v>181</v>
       </c>
       <c r="N10" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="O10" t="s">
         <v>207</v>
@@ -2090,7 +2075,7 @@
         <v>256</v>
       </c>
       <c r="R10" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -2113,7 +2098,7 @@
         <v>287</v>
       </c>
       <c r="G11" t="s">
-        <v>310</v>
+        <v>208</v>
       </c>
       <c r="H11" t="s">
         <v>94</v>
@@ -2134,7 +2119,7 @@
         <v>182</v>
       </c>
       <c r="N11" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="O11" t="s">
         <v>208</v>
@@ -2143,10 +2128,10 @@
         <v>230</v>
       </c>
       <c r="Q11" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="R11" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -2169,7 +2154,7 @@
         <v>288</v>
       </c>
       <c r="G12" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="H12" t="s">
         <v>82</v>
@@ -2178,7 +2163,7 @@
         <v>120</v>
       </c>
       <c r="J12" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="K12" t="s">
         <v>156</v>
@@ -2190,7 +2175,7 @@
         <v>183</v>
       </c>
       <c r="N12" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="O12" t="s">
         <v>76</v>
@@ -2202,7 +2187,7 @@
         <v>257</v>
       </c>
       <c r="R12" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -2225,7 +2210,7 @@
         <v>289</v>
       </c>
       <c r="G13" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="H13" t="s">
         <v>95</v>
@@ -2246,7 +2231,7 @@
         <v>184</v>
       </c>
       <c r="N13" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="O13" t="s">
         <v>77</v>
@@ -2281,7 +2266,7 @@
         <v>290</v>
       </c>
       <c r="G14" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="H14" t="s">
         <v>96</v>
@@ -2302,7 +2287,7 @@
         <v>185</v>
       </c>
       <c r="N14" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="O14" t="s">
         <v>209</v>
@@ -2337,7 +2322,7 @@
         <v>291</v>
       </c>
       <c r="G15" t="s">
-        <v>313</v>
+        <v>210</v>
       </c>
       <c r="H15" t="s">
         <v>97</v>
@@ -2393,7 +2378,7 @@
         <v>290</v>
       </c>
       <c r="G16" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="H16" t="s">
         <v>98</v>
@@ -2414,7 +2399,7 @@
         <v>187</v>
       </c>
       <c r="N16" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="O16" t="s">
         <v>211</v>
@@ -2426,7 +2411,7 @@
         <v>261</v>
       </c>
       <c r="R16" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2470,7 +2455,7 @@
         <v>188</v>
       </c>
       <c r="N17" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="O17" t="s">
         <v>212</v>
@@ -2493,19 +2478,19 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D18" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="E18" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F18" t="s">
         <v>293</v>
       </c>
       <c r="G18" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="H18" t="s">
         <v>100</v>
@@ -2526,7 +2511,7 @@
         <v>189</v>
       </c>
       <c r="N18" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="O18" t="s">
         <v>213</v>
@@ -2538,7 +2523,7 @@
         <v>263</v>
       </c>
       <c r="R18" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2570,7 +2555,7 @@
         <v>126</v>
       </c>
       <c r="J19" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="K19" t="s">
         <v>163</v>
@@ -2582,7 +2567,7 @@
         <v>190</v>
       </c>
       <c r="N19" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O19" t="s">
         <v>79</v>
@@ -2617,7 +2602,7 @@
         <v>295</v>
       </c>
       <c r="G20" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="H20" t="s">
         <v>102</v>
@@ -2626,7 +2611,7 @@
         <v>122</v>
       </c>
       <c r="J20" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K20" t="s">
         <v>164</v>
@@ -2638,7 +2623,7 @@
         <v>191</v>
       </c>
       <c r="N20" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O20" t="s">
         <v>214</v>
@@ -2650,7 +2635,7 @@
         <v>265</v>
       </c>
       <c r="R20" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2673,7 +2658,7 @@
         <v>296</v>
       </c>
       <c r="G21" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="H21" t="s">
         <v>103</v>
@@ -2682,7 +2667,7 @@
         <v>127</v>
       </c>
       <c r="J21" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="K21" t="s">
         <v>165</v>
@@ -2694,7 +2679,7 @@
         <v>192</v>
       </c>
       <c r="N21" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O21" t="s">
         <v>215</v>
@@ -2706,7 +2691,7 @@
         <v>266</v>
       </c>
       <c r="R21" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2750,7 +2735,7 @@
         <v>193</v>
       </c>
       <c r="N22" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="O22" t="s">
         <v>210</v>
@@ -2762,7 +2747,7 @@
         <v>267</v>
       </c>
       <c r="R22" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2806,7 +2791,7 @@
         <v>194</v>
       </c>
       <c r="N23" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O23" t="s">
         <v>216</v>
@@ -2818,7 +2803,7 @@
         <v>268</v>
       </c>
       <c r="R23" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2829,13 +2814,13 @@
         <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D24" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E24" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F24" t="s">
         <v>297</v>
@@ -2850,7 +2835,7 @@
         <v>130</v>
       </c>
       <c r="J24" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="K24" t="s">
         <v>168</v>
@@ -2862,7 +2847,7 @@
         <v>195</v>
       </c>
       <c r="N24" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="O24" t="s">
         <v>217</v>
@@ -2874,7 +2859,7 @@
         <v>269</v>
       </c>
       <c r="R24" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2885,13 +2870,13 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="D25" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E25" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="F25" t="s">
         <v>82</v>
@@ -2906,7 +2891,7 @@
         <v>82</v>
       </c>
       <c r="J25" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="K25" t="s">
         <v>82</v>
@@ -2941,13 +2926,13 @@
         <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="E26" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F26" t="s">
         <v>299</v>
@@ -2962,7 +2947,7 @@
         <v>131</v>
       </c>
       <c r="J26" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="K26" t="s">
         <v>169</v>
@@ -2974,7 +2959,7 @@
         <v>197</v>
       </c>
       <c r="N26" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="O26" t="s">
         <v>219</v>
@@ -2986,7 +2971,7 @@
         <v>270</v>
       </c>
       <c r="R26" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -3030,7 +3015,7 @@
         <v>198</v>
       </c>
       <c r="N27" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="O27" t="s">
         <v>220</v>
@@ -3053,13 +3038,13 @@
         <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="D28" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="E28" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="F28" t="s">
         <v>301</v>
@@ -3086,7 +3071,7 @@
         <v>199</v>
       </c>
       <c r="N28" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O28" t="s">
         <v>221</v>
@@ -3098,7 +3083,7 @@
         <v>272</v>
       </c>
       <c r="R28" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3142,7 +3127,7 @@
         <v>200</v>
       </c>
       <c r="N29" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="O29" t="s">
         <v>222</v>
